--- a/files/港岛-柴湾-海德园第2期.xlsx
+++ b/files/港岛-柴湾-海德园第2期.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E189" s="4" t="n">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E197" s="4" t="n">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E201" s="4" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E203" s="4" t="n">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E205" s="4" t="n">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E207" s="4" t="n">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E209" s="4" t="n">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E211" s="4" t="n">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E213" s="4" t="n">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E215" s="4" t="n">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E217" s="4" t="n">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E218" s="4" t="n">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E219" s="4" t="n">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E220" s="4" t="n">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E221" s="4" t="n">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E222" s="4" t="n">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E223" s="4" t="n">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E224" s="4" t="n">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E225" s="4" t="n">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E226" s="4" t="n">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E227" s="4" t="n">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E228" s="4" t="n">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E229" s="4" t="n">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E230" s="4" t="n">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E231" s="4" t="n">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E232" s="4" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E233" s="4" t="n">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E234" s="4" t="n">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E235" s="4" t="n">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E236" s="4" t="n">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E237" s="4" t="n">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E238" s="4" t="n">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E239" s="4" t="n">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E240" s="4" t="n">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E241" s="4" t="n">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E242" s="4" t="n">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E243" s="4" t="n">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E244" s="4" t="n">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E245" s="4" t="n">
@@ -17757,7 +17757,7 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E246" s="4" t="n">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E247" s="4" t="n">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E248" s="4" t="n">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E249" s="4" t="n">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E250" s="4" t="n">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E251" s="4" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E252" s="4" t="n">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E253" s="4" t="n">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E254" s="4" t="n">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E255" s="4" t="n">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E256" s="4" t="n">
@@ -18527,7 +18527,7 @@
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E257" s="4" t="n">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E258" s="4" t="n">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E259" s="4" t="n">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>null房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E260" s="4" t="n">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -18936,7 +18936,7 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>C | 868呎 (null房)
+          <t>C | 868呎 (3房)
 -
 -
 (待售)</t>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>C | 868呎 (null房)
+          <t>C | 868呎 (3房)
 -
 -
 (待售)</t>
@@ -18984,7 +18984,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19000,7 +19000,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19008,7 +19008,7 @@
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19031,7 +19031,7 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19125,7 +19125,7 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19148,7 +19148,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19179,7 +19179,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19320,7 +19320,7 @@
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19437,7 +19437,7 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19507,7 +19507,7 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19569,7 +19569,7 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 -
 -
 (待售)</t>
@@ -19671,7 +19671,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19694,7 +19694,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19710,7 +19710,7 @@
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19733,7 +19733,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>A | 1395呎 (null房)
+          <t>A | 1395呎 (4+房)
 -
 -
 (待售)</t>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>B | 784呎 (null房)
+          <t>B | 784呎 (3房)
 -
 -
 (待售)</t>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -19850,7 +19850,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -19858,7 +19858,7 @@
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19881,7 +19881,7 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19905,7 +19905,7 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -19928,7 +19928,7 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -19936,7 +19936,7 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20014,7 +20014,7 @@
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20053,7 +20053,7 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20193,7 +20193,7 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20217,7 +20217,7 @@
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20232,7 +20232,7 @@
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20295,7 +20295,7 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>A | 1393呎 (null房)
+          <t>A | 1393呎 (4+房)
 -
 -
 (待售)</t>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20326,7 +20326,7 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>C | 601呎 (null房)
+          <t>C | 601呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>D | 585呎 (null房)
+          <t>D | 585呎 (2房)
 招标单位
 -
 (在售)</t>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>A | 1339呎 (null房)
+          <t>A | 1339呎 (4+房)
 -
 -
 (待售)</t>
@@ -20357,7 +20357,7 @@
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>B | 744呎 (null房)
+          <t>B | 744呎 (3房)
 -
 -
 (待售)</t>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>C | 563呎 (null房)
+          <t>C | 563呎 (2房)
 -
 -
 (待售)</t>
@@ -20373,7 +20373,7 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>D | 547呎 (null房)
+          <t>D | 547呎 (2房)
 -
 -
 (待售)</t>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>A | 2847呎 (null房)
+          <t>A | 2847呎 (3房)
 -
 -
 (待售)</t>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>A | 1744呎 (null房)
+          <t>A | 1744呎 (4+房)
 -
 -
 (待售)</t>
@@ -20530,7 +20530,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>B | 786呎 (null房)
+          <t>B | 786呎 (3房)
 -
 -
 (待售)</t>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20554,7 +20554,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20585,7 +20585,7 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20624,7 +20624,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20655,7 +20655,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20670,7 +20670,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20701,7 +20701,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20717,7 +20717,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20740,7 +20740,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20763,7 +20763,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20833,7 +20833,7 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20872,7 +20872,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20903,7 +20903,7 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -21058,7 +21058,7 @@
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -21081,7 +21081,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -21089,7 +21089,7 @@
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -21104,7 +21104,7 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -21112,7 +21112,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -21120,7 +21120,7 @@
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -21135,7 +21135,7 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>A | 1116呎 (null房)
+          <t>A | 1116呎 (3房)
 -
 -
 (待售)</t>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>B | 789呎 (null房)
+          <t>B | 789呎 (3房)
 -
 -
 (待售)</t>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>C | 608呎 (null房)
+          <t>C | 608呎 (2房)
 -
 -
 (待售)</t>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21205,7 +21205,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21275,7 +21275,7 @@
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21298,7 +21298,7 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21383,7 +21383,7 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21391,7 +21391,7 @@
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21422,7 +21422,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21461,7 +21461,7 @@
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21476,7 +21476,7 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21492,7 +21492,7 @@
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21515,7 +21515,7 @@
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21538,7 +21538,7 @@
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21546,7 +21546,7 @@
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>A | 1120呎 (null房)
+          <t>A | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -21577,7 +21577,7 @@
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>B | 788呎 (null房)
+          <t>B | 788呎 (3房)
 -
 -
 (待售)</t>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>C | 610呎 (null房)
+          <t>C | 610呎 (2房)
 -
 -
 (待售)</t>
@@ -21600,7 +21600,7 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>A | 1068呎 (null房)
+          <t>A | 1068呎 (3房)
 -
 -
 (待售)</t>
@@ -21608,7 +21608,7 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>B | 746呎 (null房)
+          <t>B | 746呎 (3房)
 -
 -
 (待售)</t>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>C | 572呎 (null房)
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
